--- a/XAUUSD_News_Analysis.xlsx
+++ b/XAUUSD_News_Analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1652"/>
+  <dimension ref="A1:O1663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1131,27 +1131,15 @@
       <c r="D12" t="b">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>0</v>
       </c>
@@ -1190,27 +1178,15 @@
       <c r="D13" t="b">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>0</v>
       </c>
@@ -1249,27 +1225,15 @@
       <c r="D14" t="b">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
         <v>0</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>0</v>
       </c>
@@ -29746,27 +29710,15 @@
       <c r="D497" t="b">
         <v>0</v>
       </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E497" t="inlineStr"/>
       <c r="F497" t="n">
         <v>0</v>
       </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G497" t="inlineStr"/>
       <c r="H497" t="n">
         <v>0</v>
       </c>
-      <c r="I497" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I497" t="inlineStr"/>
       <c r="J497" t="n">
         <v>0</v>
       </c>
@@ -29805,27 +29757,15 @@
       <c r="D498" t="b">
         <v>0</v>
       </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E498" t="inlineStr"/>
       <c r="F498" t="n">
         <v>0</v>
       </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G498" t="inlineStr"/>
       <c r="H498" t="n">
         <v>0</v>
       </c>
-      <c r="I498" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I498" t="inlineStr"/>
       <c r="J498" t="n">
         <v>0</v>
       </c>
@@ -29864,27 +29804,15 @@
       <c r="D499" t="b">
         <v>0</v>
       </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E499" t="inlineStr"/>
       <c r="F499" t="n">
         <v>0</v>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G499" t="inlineStr"/>
       <c r="H499" t="n">
         <v>0</v>
       </c>
-      <c r="I499" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I499" t="inlineStr"/>
       <c r="J499" t="n">
         <v>0</v>
       </c>
@@ -73170,27 +73098,15 @@
       <c r="D1233" t="b">
         <v>0</v>
       </c>
-      <c r="E1233" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E1233" t="inlineStr"/>
       <c r="F1233" t="n">
         <v>0</v>
       </c>
-      <c r="G1233" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G1233" t="inlineStr"/>
       <c r="H1233" t="n">
         <v>0</v>
       </c>
-      <c r="I1233" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I1233" t="inlineStr"/>
       <c r="J1233" t="n">
         <v>0</v>
       </c>
@@ -73221,27 +73137,15 @@
       <c r="D1234" t="b">
         <v>0</v>
       </c>
-      <c r="E1234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="E1234" t="inlineStr"/>
       <c r="F1234" t="n">
         <v>0</v>
       </c>
-      <c r="G1234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G1234" t="inlineStr"/>
       <c r="H1234" t="n">
         <v>0</v>
       </c>
-      <c r="I1234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="I1234" t="inlineStr"/>
       <c r="J1234" t="n">
         <v>0</v>
       </c>
@@ -77764,11 +77668,7 @@
       <c r="F1311" t="n">
         <v>32.44</v>
       </c>
-      <c r="G1311" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="G1311" t="inlineStr"/>
       <c r="H1311" t="n">
         <v>0</v>
       </c>
@@ -77961,16 +77861,16 @@
         <v>0</v>
       </c>
       <c r="L1314" t="n">
-        <v>71.9142857142858</v>
+        <v>73.5985714285715</v>
       </c>
       <c r="M1314" t="n">
-        <v>1.002165276122367</v>
+        <v>0.9792309633339146</v>
       </c>
       <c r="N1314" t="n">
-        <v>0.129042510925705</v>
+        <v>0.1260894039092372</v>
       </c>
       <c r="O1314" t="n">
-        <v>0.3155145013905439</v>
+        <v>0.3082940274461846</v>
       </c>
     </row>
     <row r="1315">
@@ -78020,16 +77920,16 @@
         <v>0</v>
       </c>
       <c r="L1315" t="n">
-        <v>71.44071428571429</v>
+        <v>74.76285714285723</v>
       </c>
       <c r="M1315" t="n">
-        <v>0.8320185568453362</v>
+        <v>0.7950471968509946</v>
       </c>
       <c r="N1315" t="n">
-        <v>0.1293380125378686</v>
+        <v>0.1235907822830281</v>
       </c>
       <c r="O1315" t="n">
-        <v>0.1818290890548607</v>
+        <v>0.1737493789888025</v>
       </c>
     </row>
     <row r="1316">
@@ -78079,16 +77979,16 @@
         <v>0</v>
       </c>
       <c r="L1316" t="n">
-        <v>71.44071428571429</v>
+        <v>74.76285714285723</v>
       </c>
       <c r="M1316" t="n">
-        <v>0.8320185568453362</v>
+        <v>0.7950471968509946</v>
       </c>
       <c r="N1316" t="n">
-        <v>0.1293380125378686</v>
+        <v>0.1235907822830281</v>
       </c>
       <c r="O1316" t="n">
-        <v>0.1818290890548607</v>
+        <v>0.1737493789888025</v>
       </c>
     </row>
     <row r="1317">
@@ -78138,16 +78038,16 @@
         <v>0</v>
       </c>
       <c r="L1317" t="n">
-        <v>76.38571428571426</v>
+        <v>78.91785714285717</v>
       </c>
       <c r="M1317" t="n">
-        <v>0.6329717598653453</v>
+        <v>0.6126623523555231</v>
       </c>
       <c r="N1317" t="n">
-        <v>0.1714980362820274</v>
+        <v>0.1659953839887767</v>
       </c>
       <c r="O1317" t="n">
-        <v>0.1519917710865906</v>
+        <v>0.1471149929854731</v>
       </c>
     </row>
     <row r="1318">
@@ -78197,16 +78097,16 @@
         <v>0</v>
       </c>
       <c r="L1318" t="n">
-        <v>79.47</v>
+        <v>82.0021428571429</v>
       </c>
       <c r="M1318" t="n">
-        <v>0.5896564741411854</v>
+        <v>0.5714484813114636</v>
       </c>
       <c r="N1318" t="n">
-        <v>0.08493771234428087</v>
+        <v>0.08231492208391762</v>
       </c>
       <c r="O1318" t="n">
-        <v>0.1589278973197433</v>
+        <v>0.1540203653214637</v>
       </c>
     </row>
     <row r="1319">
@@ -78217,7 +78117,7 @@
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>JOLTS Job Openings</t>
+          <t>ISM Non-Manufacturing PMI</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
@@ -78256,16 +78156,16 @@
         <v>0</v>
       </c>
       <c r="L1319" t="n">
-        <v>79.47</v>
+        <v>82.0021428571429</v>
       </c>
       <c r="M1319" t="n">
-        <v>0.5573172266263999</v>
+        <v>0.5401078369032165</v>
       </c>
       <c r="N1319" t="n">
-        <v>0.07814269535673839</v>
+        <v>0.07572972831720422</v>
       </c>
       <c r="O1319" t="n">
-        <v>0.08040770101925254</v>
+        <v>0.07792479290610868</v>
       </c>
     </row>
     <row r="1320">
@@ -78276,7 +78176,7 @@
       </c>
       <c r="B1320" t="inlineStr">
         <is>
-          <t>ISM Non-Manufacturing PMI</t>
+          <t>ISM Non-Manufacturing Prices Paid</t>
         </is>
       </c>
       <c r="C1320" t="inlineStr">
@@ -78315,16 +78215,16 @@
         <v>0</v>
       </c>
       <c r="L1320" t="n">
-        <v>79.47</v>
+        <v>82.0021428571429</v>
       </c>
       <c r="M1320" t="n">
-        <v>0.5573172266263999</v>
+        <v>0.5401078369032165</v>
       </c>
       <c r="N1320" t="n">
-        <v>0.07814269535673839</v>
+        <v>0.07572972831720422</v>
       </c>
       <c r="O1320" t="n">
-        <v>0.08040770101925254</v>
+        <v>0.07792479290610868</v>
       </c>
     </row>
     <row r="1321">
@@ -78335,7 +78235,7 @@
       </c>
       <c r="B1321" t="inlineStr">
         <is>
-          <t>ISM Non-Manufacturing Prices Paid</t>
+          <t>JOLTS Job Openings</t>
         </is>
       </c>
       <c r="C1321" t="inlineStr">
@@ -78374,16 +78274,16 @@
         <v>0</v>
       </c>
       <c r="L1321" t="n">
-        <v>79.47</v>
+        <v>82.0021428571429</v>
       </c>
       <c r="M1321" t="n">
-        <v>0.5573172266263999</v>
+        <v>0.5401078369032165</v>
       </c>
       <c r="N1321" t="n">
-        <v>0.07814269535673839</v>
+        <v>0.07572972831720422</v>
       </c>
       <c r="O1321" t="n">
-        <v>0.08040770101925254</v>
+        <v>0.07792479290610868</v>
       </c>
     </row>
     <row r="1322">
@@ -78433,16 +78333,16 @@
         <v>0</v>
       </c>
       <c r="L1322" t="n">
-        <v>79.47</v>
+        <v>82.0021428571429</v>
       </c>
       <c r="M1322" t="n">
-        <v>0.5573172266263999</v>
+        <v>0.5401078369032165</v>
       </c>
       <c r="N1322" t="n">
-        <v>0.1747829369573424</v>
+        <v>0.1693858174437949</v>
       </c>
       <c r="O1322" t="n">
-        <v>0.1429470240342267</v>
+        <v>0.1385329651664154</v>
       </c>
     </row>
     <row r="1323">
@@ -78492,16 +78392,16 @@
         <v>0</v>
       </c>
       <c r="L1323" t="n">
-        <v>77.53428571428569</v>
+        <v>80.53428571428574</v>
       </c>
       <c r="M1323" t="n">
-        <v>0.366031617349007</v>
+        <v>0.3523964948380457</v>
       </c>
       <c r="N1323" t="n">
-        <v>0.1225264399159819</v>
+        <v>0.1179621811473374</v>
       </c>
       <c r="O1323" t="n">
-        <v>0.2079080222574346</v>
+        <v>0.200163195799482</v>
       </c>
     </row>
     <row r="1324">
@@ -78551,16 +78451,16 @@
         <v>0</v>
       </c>
       <c r="L1324" t="n">
-        <v>76.79428571428571</v>
+        <v>79.88357142857149</v>
       </c>
       <c r="M1324" t="n">
-        <v>0.4893593273309026</v>
+        <v>0.4704346504287486</v>
       </c>
       <c r="N1324" t="n">
-        <v>0.1177170920455391</v>
+        <v>0.1131646950472562</v>
       </c>
       <c r="O1324" t="n">
-        <v>0.2052236029466478</v>
+        <v>0.1972871232239776</v>
       </c>
     </row>
     <row r="1325">
@@ -78610,16 +78510,16 @@
         <v>0</v>
       </c>
       <c r="L1325" t="n">
-        <v>76.79428571428571</v>
+        <v>79.88357142857149</v>
       </c>
       <c r="M1325" t="n">
-        <v>0.4893593273309026</v>
+        <v>0.4704346504287486</v>
       </c>
       <c r="N1325" t="n">
-        <v>0.1177170920455391</v>
+        <v>0.1131646950472562</v>
       </c>
       <c r="O1325" t="n">
-        <v>0.2052236029466478</v>
+        <v>0.1972871232239776</v>
       </c>
     </row>
     <row r="1326">
@@ -78669,16 +78569,16 @@
         <v>0</v>
       </c>
       <c r="L1326" t="n">
-        <v>76.79428571428571</v>
+        <v>79.88357142857149</v>
       </c>
       <c r="M1326" t="n">
-        <v>0.4893593273309026</v>
+        <v>0.4704346504287486</v>
       </c>
       <c r="N1326" t="n">
-        <v>0.1177170920455391</v>
+        <v>0.1131646950472562</v>
       </c>
       <c r="O1326" t="n">
-        <v>0.2052236029466478</v>
+        <v>0.1972871232239776</v>
       </c>
     </row>
     <row r="1327">
@@ -78728,16 +78628,16 @@
         <v>0</v>
       </c>
       <c r="L1327" t="n">
-        <v>77.67857142857136</v>
+        <v>79.56214285714285</v>
       </c>
       <c r="M1327" t="n">
-        <v>0.6171586206896557</v>
+        <v>0.6025478736297774</v>
       </c>
       <c r="N1327" t="n">
-        <v>0.09603678160919549</v>
+        <v>0.09376318600913933</v>
       </c>
       <c r="O1327" t="n">
-        <v>0.08239080459770123</v>
+        <v>0.08044026681749218</v>
       </c>
     </row>
     <row r="1328">
@@ -78787,16 +78687,16 @@
         <v>0</v>
       </c>
       <c r="L1328" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1328" t="n">
-        <v>0.5667811980983689</v>
+        <v>0.554149375810845</v>
       </c>
       <c r="N1328" t="n">
-        <v>0.1149063683576897</v>
+        <v>0.1123454562638006</v>
       </c>
       <c r="O1328" t="n">
-        <v>0.2798843554751008</v>
+        <v>0.2736465877945892</v>
       </c>
     </row>
     <row r="1329">
@@ -78846,16 +78746,16 @@
         <v>0</v>
       </c>
       <c r="L1329" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1329" t="n">
-        <v>0.5667811980983689</v>
+        <v>0.554149375810845</v>
       </c>
       <c r="N1329" t="n">
-        <v>0.1149063683576897</v>
+        <v>0.1123454562638006</v>
       </c>
       <c r="O1329" t="n">
-        <v>0.2798843554751008</v>
+        <v>0.2736465877945892</v>
       </c>
     </row>
     <row r="1330">
@@ -78905,16 +78805,16 @@
         <v>0</v>
       </c>
       <c r="L1330" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1330" t="n">
-        <v>0.5667811980983689</v>
+        <v>0.554149375810845</v>
       </c>
       <c r="N1330" t="n">
-        <v>0.1149063683576897</v>
+        <v>0.1123454562638006</v>
       </c>
       <c r="O1330" t="n">
-        <v>0.2798843554751008</v>
+        <v>0.2736465877945892</v>
       </c>
     </row>
     <row r="1331">
@@ -78964,16 +78864,16 @@
         <v>0</v>
       </c>
       <c r="L1331" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1331" t="n">
-        <v>0.5667811980983689</v>
+        <v>0.554149375810845</v>
       </c>
       <c r="N1331" t="n">
-        <v>0.1149063683576897</v>
+        <v>0.1123454562638006</v>
       </c>
       <c r="O1331" t="n">
-        <v>0.2798843554751008</v>
+        <v>0.2736465877945892</v>
       </c>
     </row>
     <row r="1332">
@@ -79023,16 +78923,16 @@
         <v>0</v>
       </c>
       <c r="L1332" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1332" t="n">
-        <v>0.5667811980983689</v>
+        <v>0.554149375810845</v>
       </c>
       <c r="N1332" t="n">
-        <v>0.1149063683576897</v>
+        <v>0.1123454562638006</v>
       </c>
       <c r="O1332" t="n">
-        <v>0.2798843554751008</v>
+        <v>0.2736465877945892</v>
       </c>
     </row>
     <row r="1333">
@@ -79082,16 +78982,16 @@
         <v>0</v>
       </c>
       <c r="L1333" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1333" t="n">
-        <v>0.7006335843651424</v>
+        <v>0.685018601094587</v>
       </c>
       <c r="N1333" t="n">
-        <v>0.09165443728745058</v>
+        <v>0.08961173973932701</v>
       </c>
       <c r="O1333" t="n">
-        <v>0.1706371872720724</v>
+        <v>0.166834205393888</v>
       </c>
     </row>
     <row r="1334">
@@ -79141,16 +79041,16 @@
         <v>0</v>
       </c>
       <c r="L1334" t="n">
-        <v>81.28357142857132</v>
+        <v>83.1364285714285</v>
       </c>
       <c r="M1334" t="n">
-        <v>0.682425722997971</v>
+        <v>0.6672165373611367</v>
       </c>
       <c r="N1334" t="n">
-        <v>0.07566104554601626</v>
+        <v>0.07397479186535048</v>
       </c>
       <c r="O1334" t="n">
-        <v>0.1606720739562557</v>
+        <v>0.1570911840262565</v>
       </c>
     </row>
     <row r="1335">
@@ -79200,16 +79100,16 @@
         <v>0</v>
       </c>
       <c r="L1335" t="n">
-        <v>83.74357142857129</v>
+        <v>84.72142857142846</v>
       </c>
       <c r="M1335" t="n">
-        <v>0.2452725582347476</v>
+        <v>0.2424416153781303</v>
       </c>
       <c r="N1335" t="n">
-        <v>0.0597060755196562</v>
+        <v>0.05901694629457895</v>
       </c>
       <c r="O1335" t="n">
-        <v>0.3345928472121533</v>
+        <v>0.3307309670348204</v>
       </c>
     </row>
     <row r="1336">
@@ -79259,16 +79159,16 @@
         <v>0</v>
       </c>
       <c r="L1336" t="n">
-        <v>83.74357142857129</v>
+        <v>84.72142857142846</v>
       </c>
       <c r="M1336" t="n">
-        <v>0.2452725582347476</v>
+        <v>0.2424416153781303</v>
       </c>
       <c r="N1336" t="n">
-        <v>0.0597060755196562</v>
+        <v>0.05901694629457895</v>
       </c>
       <c r="O1336" t="n">
-        <v>0.3345928472121533</v>
+        <v>0.3307309670348204</v>
       </c>
     </row>
     <row r="1337">
@@ -79318,16 +79218,16 @@
         <v>0</v>
       </c>
       <c r="L1337" t="n">
-        <v>83.74357142857129</v>
+        <v>84.72142857142846</v>
       </c>
       <c r="M1337" t="n">
-        <v>0.2452725582347476</v>
+        <v>0.2424416153781303</v>
       </c>
       <c r="N1337" t="n">
-        <v>0.0597060755196562</v>
+        <v>0.05901694629457895</v>
       </c>
       <c r="O1337" t="n">
-        <v>0.3345928472121533</v>
+        <v>0.3307309670348204</v>
       </c>
     </row>
     <row r="1338">
@@ -79377,16 +79277,16 @@
         <v>0</v>
       </c>
       <c r="L1338" t="n">
-        <v>83.74357142857129</v>
+        <v>84.72142857142846</v>
       </c>
       <c r="M1338" t="n">
-        <v>0.5101287092399425</v>
+        <v>0.5042407891408826</v>
       </c>
       <c r="N1338" t="n">
-        <v>0.06567668307162182</v>
+        <v>0.06491864092403685</v>
       </c>
       <c r="O1338" t="n">
-        <v>0.1465187093252363</v>
+        <v>0.1448275862068967</v>
       </c>
     </row>
     <row r="1339">
@@ -79436,16 +79336,16 @@
         <v>0</v>
       </c>
       <c r="L1339" t="n">
-        <v>71.30499999999991</v>
+        <v>72.28285714285708</v>
       </c>
       <c r="M1339" t="n">
-        <v>0.5727508589860466</v>
+        <v>0.5650025692715133</v>
       </c>
       <c r="N1339" t="n">
-        <v>0.115840403898745</v>
+        <v>0.1142732914344441</v>
       </c>
       <c r="O1339" t="n">
-        <v>0.1615594979314216</v>
+        <v>0.1593738882959802</v>
       </c>
     </row>
     <row r="1340">
@@ -79495,16 +79395,16 @@
         <v>0</v>
       </c>
       <c r="L1340" t="n">
-        <v>71.30499999999991</v>
+        <v>72.28285714285708</v>
       </c>
       <c r="M1340" t="n">
-        <v>0.5727508589860466</v>
+        <v>0.5650025692715133</v>
       </c>
       <c r="N1340" t="n">
-        <v>0.115840403898745</v>
+        <v>0.1142732914344441</v>
       </c>
       <c r="O1340" t="n">
-        <v>0.1615594979314216</v>
+        <v>0.1593738882959802</v>
       </c>
     </row>
     <row r="1341">
@@ -79554,16 +79454,16 @@
         <v>0</v>
       </c>
       <c r="L1341" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1341" t="n">
-        <v>0.3620074391556369</v>
+        <v>0.3535073244033079</v>
       </c>
       <c r="N1341" t="n">
-        <v>0.09793629514944394</v>
+        <v>0.09563670222082918</v>
       </c>
       <c r="O1341" t="n">
-        <v>0.2594452731151936</v>
+        <v>0.253353369041144</v>
       </c>
     </row>
     <row r="1342">
@@ -79613,16 +79513,16 @@
         <v>0</v>
       </c>
       <c r="L1342" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1342" t="n">
-        <v>0.3620074391556369</v>
+        <v>0.3535073244033079</v>
       </c>
       <c r="N1342" t="n">
-        <v>0.09793629514944394</v>
+        <v>0.09563670222082918</v>
       </c>
       <c r="O1342" t="n">
-        <v>0.2594452731151936</v>
+        <v>0.253353369041144</v>
       </c>
     </row>
     <row r="1343">
@@ -79672,16 +79572,16 @@
         <v>0</v>
       </c>
       <c r="L1343" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1343" t="n">
-        <v>0.3620074391556369</v>
+        <v>0.3535073244033079</v>
       </c>
       <c r="N1343" t="n">
-        <v>0.09793629514944394</v>
+        <v>0.09563670222082918</v>
       </c>
       <c r="O1343" t="n">
-        <v>0.2594452731151936</v>
+        <v>0.253353369041144</v>
       </c>
     </row>
     <row r="1344">
@@ -79731,16 +79631,16 @@
         <v>0</v>
       </c>
       <c r="L1344" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1344" t="n">
-        <v>0.8337141022978304</v>
+        <v>0.8141380804439817</v>
       </c>
       <c r="N1344" t="n">
-        <v>0.1560901006362932</v>
+        <v>0.1524250274261799</v>
       </c>
       <c r="O1344" t="n">
-        <v>0.1534467458414364</v>
+        <v>0.1498437399168457</v>
       </c>
     </row>
     <row r="1345">
@@ -79790,16 +79690,16 @@
         <v>0</v>
       </c>
       <c r="L1345" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1345" t="n">
-        <v>0.8337141022978304</v>
+        <v>0.8141380804439817</v>
       </c>
       <c r="N1345" t="n">
-        <v>0.1560901006362932</v>
+        <v>0.1524250274261799</v>
       </c>
       <c r="O1345" t="n">
-        <v>0.1534467458414364</v>
+        <v>0.1498437399168457</v>
       </c>
     </row>
     <row r="1346">
@@ -79849,16 +79749,16 @@
         <v>0</v>
       </c>
       <c r="L1346" t="n">
-        <v>75.66142857142859</v>
+        <v>77.48071428571426</v>
       </c>
       <c r="M1346" t="n">
-        <v>1.255197024337745</v>
+        <v>1.225724373807307</v>
       </c>
       <c r="N1346" t="n">
-        <v>0.06727337952910521</v>
+        <v>0.06569376711255338</v>
       </c>
       <c r="O1346" t="n">
-        <v>0.183448822763061</v>
+        <v>0.179141353147788</v>
       </c>
     </row>
     <row r="1347">
@@ -79908,16 +79808,16 @@
         <v>0</v>
       </c>
       <c r="L1347" t="n">
-        <v>81.48571428571424</v>
+        <v>80.99214285714275</v>
       </c>
       <c r="M1347" t="n">
-        <v>0.5382538569424968</v>
+        <v>0.5415340112356585</v>
       </c>
       <c r="N1347" t="n">
-        <v>0.1397791023842918</v>
+        <v>0.1406309253984074</v>
       </c>
       <c r="O1347" t="n">
-        <v>0.1995441795231418</v>
+        <v>0.2007602148356545</v>
       </c>
     </row>
     <row r="1348">
@@ -79967,16 +79867,16 @@
         <v>0</v>
       </c>
       <c r="L1348" t="n">
-        <v>85.05071428571416</v>
+        <v>84.55714285714268</v>
       </c>
       <c r="M1348" t="n">
-        <v>0.6218642658581863</v>
+        <v>0.6254941713127231</v>
       </c>
       <c r="N1348" t="n">
-        <v>0.1062895247373417</v>
+        <v>0.1069099510052376</v>
       </c>
       <c r="O1348" t="n">
-        <v>0.2010565125009451</v>
+        <v>0.2022301064368986</v>
       </c>
     </row>
     <row r="1349">
@@ -80026,16 +79926,16 @@
         <v>0</v>
       </c>
       <c r="L1349" t="n">
-        <v>91.25428571428567</v>
+        <v>90.56999999999991</v>
       </c>
       <c r="M1349" t="n">
-        <v>0.6863239299915467</v>
+        <v>0.6915093298001553</v>
       </c>
       <c r="N1349" t="n">
-        <v>0.08887253827608883</v>
+        <v>0.08954399911670539</v>
       </c>
       <c r="O1349" t="n">
-        <v>0.2333041109615205</v>
+        <v>0.2350667991608703</v>
       </c>
     </row>
     <row r="1350">
@@ -80085,16 +79985,16 @@
         <v>0</v>
       </c>
       <c r="L1350" t="n">
-        <v>91.25428571428567</v>
+        <v>90.56999999999991</v>
       </c>
       <c r="M1350" t="n">
-        <v>0.6285732176962338</v>
+        <v>0.6333222921497191</v>
       </c>
       <c r="N1350" t="n">
-        <v>0.2319891042299385</v>
+        <v>0.2337418571270843</v>
       </c>
       <c r="O1350" t="n">
-        <v>0.1951689157456402</v>
+        <v>0.1966434801810756</v>
       </c>
     </row>
     <row r="1351">
@@ -80144,16 +80044,16 @@
         <v>0</v>
       </c>
       <c r="L1351" t="n">
-        <v>99.43071428571427</v>
+        <v>98.94357142857136</v>
       </c>
       <c r="M1351" t="n">
-        <v>0.8465191123754517</v>
+        <v>0.8506868994592883</v>
       </c>
       <c r="N1351" t="n">
-        <v>0.3293750853070695</v>
+        <v>0.3309967441759735</v>
       </c>
       <c r="O1351" t="n">
-        <v>0.5519421276840298</v>
+        <v>0.5546595823016008</v>
       </c>
     </row>
     <row r="1352">
@@ -80203,16 +80103,16 @@
         <v>0</v>
       </c>
       <c r="L1352" t="n">
-        <v>130.3828571428571</v>
+        <v>129.8957142857142</v>
       </c>
       <c r="M1352" t="n">
-        <v>1.811741245562519</v>
+        <v>1.818535748457555</v>
       </c>
       <c r="N1352" t="n">
-        <v>0.2974317394924837</v>
+        <v>0.2985471862043179</v>
       </c>
       <c r="O1352" t="n">
-        <v>0.4413156856729632</v>
+        <v>0.4429707347652515</v>
       </c>
     </row>
     <row r="1353">
@@ -80262,16 +80162,16 @@
         <v>0</v>
       </c>
       <c r="L1353" t="n">
-        <v>130.3828571428571</v>
+        <v>129.8957142857142</v>
       </c>
       <c r="M1353" t="n">
-        <v>1.554192049787439</v>
+        <v>1.560020675926843</v>
       </c>
       <c r="N1353" t="n">
-        <v>0.209613446114739</v>
+        <v>0.2103995512883963</v>
       </c>
       <c r="O1353" t="n">
-        <v>0.3974448875838191</v>
+        <v>0.3989354097242845</v>
       </c>
     </row>
     <row r="1354">
@@ -80321,16 +80221,16 @@
         <v>0</v>
       </c>
       <c r="L1354" t="n">
-        <v>178.2257142857142</v>
+        <v>182.4192857142856</v>
       </c>
       <c r="M1354" t="n">
-        <v>1.030266596130108</v>
+        <v>1.006582167455666</v>
       </c>
       <c r="N1354" t="n">
-        <v>0.2587729844979882</v>
+        <v>0.2528241453167155</v>
       </c>
       <c r="O1354" t="n">
-        <v>0.606141489924494</v>
+        <v>0.5922071209576057</v>
       </c>
     </row>
     <row r="1355">
@@ -80380,16 +80280,16 @@
         <v>0</v>
       </c>
       <c r="L1355" t="n">
-        <v>178.2257142857142</v>
+        <v>182.4192857142856</v>
       </c>
       <c r="M1355" t="n">
-        <v>1.030266596130108</v>
+        <v>1.006582167455666</v>
       </c>
       <c r="N1355" t="n">
-        <v>0.2587729844979882</v>
+        <v>0.2528241453167155</v>
       </c>
       <c r="O1355" t="n">
-        <v>0.606141489924494</v>
+        <v>0.5922071209576057</v>
       </c>
     </row>
     <row r="1356">
@@ -80439,16 +80339,16 @@
         <v>0</v>
       </c>
       <c r="L1356" t="n">
-        <v>232.325</v>
+        <v>234.1271428571428</v>
       </c>
       <c r="M1356" t="n">
-        <v>0.3386204670181858</v>
+        <v>0.3360140094820275</v>
       </c>
       <c r="N1356" t="n">
-        <v>0.08742063919078878</v>
+        <v>0.08674773779814386</v>
       </c>
       <c r="O1356" t="n">
-        <v>0.2032928010330357</v>
+        <v>0.2017279988284754</v>
       </c>
     </row>
     <row r="1357">
@@ -80498,16 +80398,16 @@
         <v>0</v>
       </c>
       <c r="L1357" t="n">
-        <v>232.325</v>
+        <v>234.1271428571428</v>
       </c>
       <c r="M1357" t="n">
-        <v>0.7703863122780589</v>
+        <v>0.764456430876996</v>
       </c>
       <c r="N1357" t="n">
-        <v>0.1729904228989562</v>
+        <v>0.1716588666719548</v>
       </c>
       <c r="O1357" t="n">
-        <v>0.1927902722479286</v>
+        <v>0.1913063109787722</v>
       </c>
     </row>
     <row r="1358">
@@ -80557,16 +80457,16 @@
         <v>0</v>
       </c>
       <c r="L1358" t="n">
-        <v>232.325</v>
+        <v>234.1271428571428</v>
       </c>
       <c r="M1358" t="n">
-        <v>0.7703863122780589</v>
+        <v>0.764456430876996</v>
       </c>
       <c r="N1358" t="n">
-        <v>0.1729904228989562</v>
+        <v>0.1716588666719548</v>
       </c>
       <c r="O1358" t="n">
-        <v>0.1927902722479286</v>
+        <v>0.1913063109787722</v>
       </c>
     </row>
     <row r="1359">
@@ -80616,16 +80516,16 @@
         <v>0</v>
       </c>
       <c r="L1359" t="n">
-        <v>232.325</v>
+        <v>234.1271428571428</v>
       </c>
       <c r="M1359" t="n">
-        <v>0.7615624663725387</v>
+        <v>0.7557005046098274</v>
       </c>
       <c r="N1359" t="n">
-        <v>0.159087485203917</v>
+        <v>0.157862943821733</v>
       </c>
       <c r="O1359" t="n">
-        <v>0.3486925642957066</v>
+        <v>0.3460085789772346</v>
       </c>
     </row>
     <row r="1360">
@@ -80675,16 +80575,16 @@
         <v>0</v>
       </c>
       <c r="L1360" t="n">
-        <v>242.6157142857143</v>
+        <v>242.5121428571429</v>
       </c>
       <c r="M1360" t="n">
-        <v>0.5826498106941607</v>
+        <v>0.5828986471958695</v>
       </c>
       <c r="N1360" t="n">
-        <v>0.1155324999558384</v>
+        <v>0.115581841262735</v>
       </c>
       <c r="O1360" t="n">
-        <v>0.2528278111769936</v>
+        <v>0.2529357881932274</v>
       </c>
     </row>
     <row r="1361">
@@ -80734,16 +80634,16 @@
         <v>0</v>
       </c>
       <c r="L1361" t="n">
-        <v>242.6157142857143</v>
+        <v>242.5121428571429</v>
       </c>
       <c r="M1361" t="n">
-        <v>0.3897109479423662</v>
+        <v>0.3898773846375881</v>
       </c>
       <c r="N1361" t="n">
-        <v>0.07324340079255259</v>
+        <v>0.07327468138561545</v>
       </c>
       <c r="O1361" t="n">
-        <v>0.1189535479388333</v>
+        <v>0.1190043502976287</v>
       </c>
     </row>
     <row r="1362">
@@ -80793,16 +80693,16 @@
         <v>0</v>
       </c>
       <c r="L1362" t="n">
-        <v>257.3335714285714</v>
+        <v>258.2928571428571</v>
       </c>
       <c r="M1362" t="n">
-        <v>0.2151681947000419</v>
+        <v>0.2143690716517795</v>
       </c>
       <c r="N1362" t="n">
-        <v>0.02455956276872431</v>
+        <v>0.02446834987970466</v>
       </c>
       <c r="O1362" t="n">
-        <v>0.2236396894525449</v>
+        <v>0.2228091037305384</v>
       </c>
     </row>
     <row r="1363">
@@ -80852,16 +80752,16 @@
         <v>0</v>
       </c>
       <c r="L1363" t="n">
-        <v>257.3335714285714</v>
+        <v>258.2928571428571</v>
       </c>
       <c r="M1363" t="n">
-        <v>0.2151681947000419</v>
+        <v>0.2143690716517795</v>
       </c>
       <c r="N1363" t="n">
-        <v>0.02455956276872431</v>
+        <v>0.02446834987970466</v>
       </c>
       <c r="O1363" t="n">
-        <v>0.2236396894525449</v>
+        <v>0.2228091037305384</v>
       </c>
     </row>
     <row r="1364">
@@ -80911,16 +80811,16 @@
         <v>0</v>
       </c>
       <c r="L1364" t="n">
-        <v>262.1035714285714</v>
+        <v>263.0628571428571</v>
       </c>
       <c r="M1364" t="n">
-        <v>0.3829020697924758</v>
+        <v>0.3815057780867148</v>
       </c>
       <c r="N1364" t="n">
-        <v>0.05482565507092344</v>
+        <v>0.05462572769137197</v>
       </c>
       <c r="O1364" t="n">
-        <v>0.1566174767335704</v>
+        <v>0.156046355026501</v>
       </c>
     </row>
     <row r="1365">
@@ -80970,16 +80870,16 @@
         <v>0</v>
       </c>
       <c r="L1365" t="n">
-        <v>262.1035714285714</v>
+        <v>263.0628571428571</v>
       </c>
       <c r="M1365" t="n">
-        <v>0.3829020697924758</v>
+        <v>0.3815057780867148</v>
       </c>
       <c r="N1365" t="n">
-        <v>0.05482565507092344</v>
+        <v>0.05462572769137197</v>
       </c>
       <c r="O1365" t="n">
-        <v>0.1566174767335704</v>
+        <v>0.156046355026501</v>
       </c>
     </row>
     <row r="1366">
@@ -81029,16 +80929,16 @@
         <v>0</v>
       </c>
       <c r="L1366" t="n">
-        <v>262.1035714285714</v>
+        <v>263.0628571428571</v>
       </c>
       <c r="M1366" t="n">
-        <v>0.3829020697924758</v>
+        <v>0.3815057780867148</v>
       </c>
       <c r="N1366" t="n">
-        <v>0.05482565507092344</v>
+        <v>0.05462572769137197</v>
       </c>
       <c r="O1366" t="n">
-        <v>0.1566174767335704</v>
+        <v>0.156046355026501</v>
       </c>
     </row>
     <row r="1367">
@@ -81088,16 +80988,16 @@
         <v>0</v>
       </c>
       <c r="L1367" t="n">
-        <v>262.1035714285714</v>
+        <v>263.0628571428571</v>
       </c>
       <c r="M1367" t="n">
-        <v>0.3829020697924758</v>
+        <v>0.3815057780867148</v>
       </c>
       <c r="N1367" t="n">
-        <v>0.0427693523552576</v>
+        <v>0.04261338952124425</v>
       </c>
       <c r="O1367" t="n">
-        <v>0.08328768616550164</v>
+        <v>0.08298396906768615</v>
       </c>
     </row>
     <row r="1368">
@@ -81147,16 +81047,16 @@
         <v>0</v>
       </c>
       <c r="L1368" t="n">
-        <v>262.1035714285714</v>
+        <v>263.0628571428571</v>
       </c>
       <c r="M1368" t="n">
-        <v>0.3055662292714167</v>
+        <v>0.3044519506473195</v>
       </c>
       <c r="N1368" t="n">
-        <v>0.029721075365518</v>
+        <v>0.02961269441306804</v>
       </c>
       <c r="O1368" t="n">
-        <v>0.04055648666693919</v>
+        <v>0.0404085932748284</v>
       </c>
     </row>
     <row r="1369">
@@ -81206,16 +81106,16 @@
         <v>0</v>
       </c>
       <c r="L1369" t="n">
-        <v>261.5592857142857</v>
+        <v>262.5185714285715</v>
       </c>
       <c r="M1369" t="n">
-        <v>0.1333540879833307</v>
+        <v>0.1328667903767352</v>
       </c>
       <c r="N1369" t="n">
-        <v>0.03433256049570842</v>
+        <v>0.0342071037151113</v>
       </c>
       <c r="O1369" t="n">
-        <v>0.07608217749048971</v>
+        <v>0.07580416079406624</v>
       </c>
     </row>
     <row r="1370">
@@ -81265,16 +81165,16 @@
         <v>0</v>
       </c>
       <c r="L1370" t="n">
-        <v>261.5592857142857</v>
+        <v>262.5185714285715</v>
       </c>
       <c r="M1370" t="n">
-        <v>0.1692541707288432</v>
+        <v>0.1686356883594629</v>
       </c>
       <c r="N1370" t="n">
-        <v>0.05279873724340015</v>
+        <v>0.05260580203849521</v>
       </c>
       <c r="O1370" t="n">
-        <v>0.5896177594262977</v>
+        <v>0.5874631998824571</v>
       </c>
     </row>
     <row r="1371">
@@ -81324,16 +81224,16 @@
         <v>0</v>
       </c>
       <c r="L1371" t="n">
-        <v>261.5592857142857</v>
+        <v>262.5185714285715</v>
       </c>
       <c r="M1371" t="n">
-        <v>0.7839905184020011</v>
+        <v>0.7811256890668956</v>
       </c>
       <c r="N1371" t="n">
-        <v>0.07218248799097718</v>
+        <v>0.07191872139658144</v>
       </c>
       <c r="O1371" t="n">
-        <v>0.05715721374285534</v>
+        <v>0.05694835195333117</v>
       </c>
     </row>
     <row r="1372">
@@ -81383,16 +81283,16 @@
         <v>0</v>
       </c>
       <c r="L1372" t="n">
-        <v>269.0935714285715</v>
+        <v>258.5678571428572</v>
       </c>
       <c r="M1372" t="n">
-        <v>0.2753688971706602</v>
+        <v>0.28657854390254</v>
       </c>
       <c r="N1372" t="n">
-        <v>0.02943214123605437</v>
+        <v>0.03063025732399618</v>
       </c>
       <c r="O1372" t="n">
-        <v>0.1720962702830401</v>
+        <v>0.1791019212972555</v>
       </c>
     </row>
     <row r="1373">
@@ -81442,16 +81342,16 @@
         <v>0</v>
       </c>
       <c r="L1373" t="n">
-        <v>269.0935714285715</v>
+        <v>258.5678571428572</v>
       </c>
       <c r="M1373" t="n">
-        <v>0.2753688971706602</v>
+        <v>0.28657854390254</v>
       </c>
       <c r="N1373" t="n">
-        <v>0.02943214123605437</v>
+        <v>0.03063025732399618</v>
       </c>
       <c r="O1373" t="n">
-        <v>0.1720962702830401</v>
+        <v>0.1791019212972555</v>
       </c>
     </row>
     <row r="1374">
@@ -81501,16 +81401,16 @@
         <v>0</v>
       </c>
       <c r="L1374" t="n">
-        <v>269.0935714285715</v>
+        <v>258.5678571428572</v>
       </c>
       <c r="M1374" t="n">
-        <v>0.2753688971706602</v>
+        <v>0.28657854390254</v>
       </c>
       <c r="N1374" t="n">
-        <v>0.02943214123605437</v>
+        <v>0.03063025732399618</v>
       </c>
       <c r="O1374" t="n">
-        <v>0.1720962702830401</v>
+        <v>0.1791019212972555</v>
       </c>
     </row>
     <row r="1375">
@@ -81560,16 +81460,16 @@
         <v>0</v>
       </c>
       <c r="L1375" t="n">
-        <v>269.0935714285715</v>
+        <v>258.5678571428572</v>
       </c>
       <c r="M1375" t="n">
-        <v>0.2753688971706602</v>
+        <v>0.28657854390254</v>
       </c>
       <c r="N1375" t="n">
-        <v>0.02943214123605437</v>
+        <v>0.03063025732399618</v>
       </c>
       <c r="O1375" t="n">
-        <v>0.1720962702830401</v>
+        <v>0.1791019212972555</v>
       </c>
     </row>
     <row r="1376">
@@ -81619,16 +81519,16 @@
         <v>0</v>
       </c>
       <c r="L1376" t="n">
-        <v>269.0935714285715</v>
+        <v>258.5678571428572</v>
       </c>
       <c r="M1376" t="n">
-        <v>0.2753688971706602</v>
+        <v>0.28657854390254</v>
       </c>
       <c r="N1376" t="n">
-        <v>0.02943214123605437</v>
+        <v>0.03063025732399618</v>
       </c>
       <c r="O1376" t="n">
-        <v>0.1720962702830401</v>
+        <v>0.1791019212972555</v>
       </c>
     </row>
     <row r="1377">
@@ -81678,16 +81578,16 @@
         <v>0</v>
       </c>
       <c r="L1377" t="n">
-        <v>190.4442857142857</v>
+        <v>180.4207142857143</v>
       </c>
       <c r="M1377" t="n">
-        <v>0.3283374965306688</v>
+        <v>0.3465788296402456</v>
       </c>
       <c r="N1377" t="n">
-        <v>0.0425846329260151</v>
+        <v>0.04495049269762341</v>
       </c>
       <c r="O1377" t="n">
-        <v>0.176009481588166</v>
+        <v>0.185787979682409</v>
       </c>
     </row>
     <row r="1378">
@@ -81737,16 +81637,16 @@
         <v>0</v>
       </c>
       <c r="L1378" t="n">
-        <v>167.0407142857143</v>
+        <v>156.8785714285714</v>
       </c>
       <c r="M1378" t="n">
-        <v>0.3004656691910014</v>
+        <v>0.3199289714519874</v>
       </c>
       <c r="N1378" t="n">
-        <v>0.02256934793484908</v>
+        <v>0.02403132541091836</v>
       </c>
       <c r="O1378" t="n">
-        <v>0.2137203504705868</v>
+        <v>0.2275645403633383</v>
       </c>
     </row>
     <row r="1379">
@@ -81796,16 +81696,16 @@
         <v>0</v>
       </c>
       <c r="L1379" t="n">
-        <v>167.0407142857143</v>
+        <v>156.8785714285714</v>
       </c>
       <c r="M1379" t="n">
-        <v>0.3004656691910014</v>
+        <v>0.3199289714519874</v>
       </c>
       <c r="N1379" t="n">
-        <v>0.02256934793484908</v>
+        <v>0.02403132541091836</v>
       </c>
       <c r="O1379" t="n">
-        <v>0.2137203504705868</v>
+        <v>0.2275645403633383</v>
       </c>
     </row>
     <row r="1380">
@@ -81855,16 +81755,16 @@
         <v>0</v>
       </c>
       <c r="L1380" t="n">
-        <v>167.0407142857143</v>
+        <v>156.8785714285714</v>
       </c>
       <c r="M1380" t="n">
-        <v>0.3478193939031118</v>
+        <v>0.3703501343168055</v>
       </c>
       <c r="N1380" t="n">
-        <v>0.06028470390024674</v>
+        <v>0.06418977371033101</v>
       </c>
       <c r="O1380" t="n">
-        <v>0.05699209345882313</v>
+        <v>0.06068387743022356</v>
       </c>
     </row>
     <row r="1381">
@@ -81914,16 +81814,16 @@
         <v>0</v>
       </c>
       <c r="L1381" t="n">
-        <v>144.6557142857143</v>
+        <v>135.9578571428571</v>
       </c>
       <c r="M1381" t="n">
-        <v>0.3016126961554035</v>
+        <v>0.3209082646408289</v>
       </c>
       <c r="N1381" t="n">
-        <v>0.03276745770746305</v>
+        <v>0.03486374454268917</v>
       </c>
       <c r="O1381" t="n">
-        <v>0.1580995269556287</v>
+        <v>0.1682138898082914</v>
       </c>
     </row>
     <row r="1382">
@@ -81973,16 +81873,16 @@
         <v>0</v>
       </c>
       <c r="L1382" t="n">
-        <v>144.6557142857143</v>
+        <v>135.9578571428571</v>
       </c>
       <c r="M1382" t="n">
-        <v>0.3016126961554035</v>
+        <v>0.3209082646408289</v>
       </c>
       <c r="N1382" t="n">
-        <v>0.03276745770746305</v>
+        <v>0.03486374454268917</v>
       </c>
       <c r="O1382" t="n">
-        <v>0.1580995269556287</v>
+        <v>0.1682138898082914</v>
       </c>
     </row>
     <row r="1383">
@@ -82032,16 +81932,16 @@
         <v>0</v>
       </c>
       <c r="L1383" t="n">
-        <v>144.6557142857143</v>
+        <v>135.9578571428571</v>
       </c>
       <c r="M1383" t="n">
-        <v>0.3016126961554035</v>
+        <v>0.3209082646408289</v>
       </c>
       <c r="N1383" t="n">
-        <v>0.03276745770746305</v>
+        <v>0.03486374454268917</v>
       </c>
       <c r="O1383" t="n">
-        <v>0.1580995269556287</v>
+        <v>0.1682138898082914</v>
       </c>
     </row>
     <row r="1384">
@@ -82091,16 +81991,16 @@
         <v>0</v>
       </c>
       <c r="L1384" t="n">
-        <v>144.6557142857143</v>
+        <v>135.9578571428571</v>
       </c>
       <c r="M1384" t="n">
-        <v>0.3016126961554035</v>
+        <v>0.3209082646408289</v>
       </c>
       <c r="N1384" t="n">
-        <v>0.03276745770746305</v>
+        <v>0.03486374454268917</v>
       </c>
       <c r="O1384" t="n">
-        <v>0.1580995269556287</v>
+        <v>0.1682138898082914</v>
       </c>
     </row>
     <row r="1385">
@@ -82150,16 +82050,16 @@
         <v>0</v>
       </c>
       <c r="L1385" t="n">
-        <v>144.6557142857143</v>
+        <v>135.9578571428571</v>
       </c>
       <c r="M1385" t="n">
-        <v>0.5063747419982423</v>
+        <v>0.5387698919307979</v>
       </c>
       <c r="N1385" t="n">
-        <v>0.0841999229698101</v>
+        <v>0.0895865840780494</v>
       </c>
       <c r="O1385" t="n">
-        <v>0.122428623628517</v>
+        <v>0.1302609527111868</v>
       </c>
     </row>
     <row r="1386">
@@ -82209,16 +82109,16 @@
         <v>0</v>
       </c>
       <c r="L1386" t="n">
-        <v>107.9528571428571</v>
+        <v>100.8892857142856</v>
       </c>
       <c r="M1386" t="n">
-        <v>0.83008456072095</v>
+        <v>0.8882013522602576</v>
       </c>
       <c r="N1386" t="n">
-        <v>0.07012320192676702</v>
+        <v>0.07503274452193004</v>
       </c>
       <c r="O1386" t="n">
-        <v>0.101247899215266</v>
+        <v>0.1083365782859571</v>
       </c>
     </row>
     <row r="1387">
@@ -82268,16 +82168,16 @@
         <v>0</v>
       </c>
       <c r="L1387" t="n">
-        <v>116.7457142857142</v>
+        <v>108.5985714285714</v>
       </c>
       <c r="M1387" t="n">
-        <v>0.4327353711362917</v>
+        <v>0.4651994896012842</v>
       </c>
       <c r="N1387" t="n">
-        <v>0.07717628056092612</v>
+        <v>0.08296610058011816</v>
       </c>
       <c r="O1387" t="n">
-        <v>0.1247154988864689</v>
+        <v>0.1340717452215894</v>
       </c>
     </row>
     <row r="1388">
@@ -82327,16 +82227,16 @@
         <v>0</v>
       </c>
       <c r="L1388" t="n">
-        <v>115.0564285714286</v>
+        <v>108.1099999999999</v>
       </c>
       <c r="M1388" t="n">
-        <v>0.2875110970393409</v>
+        <v>0.305984645268708</v>
       </c>
       <c r="N1388" t="n">
-        <v>0.07596272636408223</v>
+        <v>0.0808435852372584</v>
       </c>
       <c r="O1388" t="n">
-        <v>0.3164534172673036</v>
+        <v>0.3367866062343911</v>
       </c>
     </row>
     <row r="1389">
@@ -82386,16 +82286,16 @@
         <v>0</v>
       </c>
       <c r="L1389" t="n">
-        <v>114.2185714285715</v>
+        <v>107.2721428571428</v>
       </c>
       <c r="M1389" t="n">
-        <v>0.6285317624104161</v>
+        <v>0.6692324594988717</v>
       </c>
       <c r="N1389" t="n">
-        <v>0.09735719735344513</v>
+        <v>0.1036615816914257</v>
       </c>
       <c r="O1389" t="n">
-        <v>0.1758908358660713</v>
+        <v>0.1872806813112179</v>
       </c>
     </row>
     <row r="1390">
@@ -82445,16 +82345,16 @@
         <v>0</v>
       </c>
       <c r="L1390" t="n">
-        <v>114.2185714285715</v>
+        <v>107.2721428571428</v>
       </c>
       <c r="M1390" t="n">
-        <v>0.6285317624104161</v>
+        <v>0.6692324594988717</v>
       </c>
       <c r="N1390" t="n">
-        <v>0.07923405000437757</v>
+        <v>0.08436486639455061</v>
       </c>
       <c r="O1390" t="n">
-        <v>0.1446349730466649</v>
+        <v>0.1540008389876217</v>
       </c>
     </row>
     <row r="1391">
@@ -82504,16 +82404,16 @@
         <v>0</v>
       </c>
       <c r="L1391" t="n">
-        <v>101.4007142857143</v>
+        <v>105.1471428571428</v>
       </c>
       <c r="M1391" t="n">
-        <v>1.095357175562303</v>
+        <v>1.056329225710909</v>
       </c>
       <c r="N1391" t="n">
-        <v>0.126231852410169</v>
+        <v>0.1217341684442211</v>
       </c>
       <c r="O1391" t="n">
-        <v>0.8336233190805928</v>
+        <v>0.8039210358273442</v>
       </c>
     </row>
     <row r="1392">
@@ -82563,16 +82463,16 @@
         <v>0</v>
       </c>
       <c r="L1392" t="n">
-        <v>101.4007142857143</v>
+        <v>105.1471428571428</v>
       </c>
       <c r="M1392" t="n">
-        <v>1.095357175562303</v>
+        <v>1.056329225710909</v>
       </c>
       <c r="N1392" t="n">
-        <v>0.2831341002106213</v>
+        <v>0.273045935627624</v>
       </c>
       <c r="O1392" t="n">
-        <v>0.5380632708983455</v>
+        <v>0.5188918929934923</v>
       </c>
     </row>
     <row r="1393">
@@ -82622,16 +82522,16 @@
         <v>0</v>
       </c>
       <c r="L1393" t="n">
-        <v>101.4007142857143</v>
+        <v>105.1471428571428</v>
       </c>
       <c r="M1393" t="n">
-        <v>1.095357175562303</v>
+        <v>1.056329225710909</v>
       </c>
       <c r="N1393" t="n">
-        <v>0.2831341002106213</v>
+        <v>0.273045935627624</v>
       </c>
       <c r="O1393" t="n">
-        <v>0.5380632708983455</v>
+        <v>0.5188918929934923</v>
       </c>
     </row>
     <row r="1394">
@@ -82681,16 +82581,16 @@
         <v>0</v>
       </c>
       <c r="L1394" t="n">
-        <v>126.71</v>
+        <v>123.9685714285715</v>
       </c>
       <c r="M1394" t="n">
-        <v>0.458369505169284</v>
+        <v>0.4685058424946414</v>
       </c>
       <c r="N1394" t="n">
-        <v>0.1223265724883592</v>
+        <v>0.1250316900596925</v>
       </c>
       <c r="O1394" t="n">
-        <v>0.1961171178281114</v>
+        <v>0.2004540321279587</v>
       </c>
     </row>
     <row r="1395">
@@ -82740,16 +82640,16 @@
         <v>0</v>
       </c>
       <c r="L1395" t="n">
-        <v>126.71</v>
+        <v>123.9685714285715</v>
       </c>
       <c r="M1395" t="n">
-        <v>0.5900086812406281</v>
+        <v>0.6030560741201686</v>
       </c>
       <c r="N1395" t="n">
-        <v>0.2317102044037565</v>
+        <v>0.2368342206550047</v>
       </c>
       <c r="O1395" t="n">
-        <v>0.2308420803409359</v>
+        <v>0.2359468989836133</v>
       </c>
     </row>
     <row r="1396">
@@ -82799,16 +82699,16 @@
         <v>0</v>
       </c>
       <c r="L1396" t="n">
-        <v>126.71</v>
+        <v>123.9685714285715</v>
       </c>
       <c r="M1396" t="n">
-        <v>0.5900086812406281</v>
+        <v>0.6030560741201686</v>
       </c>
       <c r="N1396" t="n">
-        <v>0.1162497040486149</v>
+        <v>0.118820438359953</v>
       </c>
       <c r="O1396" t="n">
-        <v>0.1566569331544471</v>
+        <v>0.1601212288828966</v>
       </c>
     </row>
     <row r="1397">
@@ -82858,16 +82758,16 @@
         <v>0</v>
       </c>
       <c r="L1397" t="n">
-        <v>126.71</v>
+        <v>123.9685714285715</v>
       </c>
       <c r="M1397" t="n">
-        <v>0.5900086812406281</v>
+        <v>0.6030560741201686</v>
       </c>
       <c r="N1397" t="n">
-        <v>0.1162497040486149</v>
+        <v>0.118820438359953</v>
       </c>
       <c r="O1397" t="n">
-        <v>0.1566569331544471</v>
+        <v>0.1601212288828966</v>
       </c>
     </row>
     <row r="1398">
@@ -82917,16 +82817,16 @@
         <v>0</v>
       </c>
       <c r="L1398" t="n">
-        <v>126.71</v>
+        <v>123.9685714285715</v>
       </c>
       <c r="M1398" t="n">
-        <v>0.5900086812406281</v>
+        <v>0.6030560741201686</v>
       </c>
       <c r="N1398" t="n">
-        <v>0.1382684870965196</v>
+        <v>0.1413261425706976</v>
       </c>
       <c r="O1398" t="n">
-        <v>0.1284034409281035</v>
+        <v>0.1312429417594321</v>
       </c>
     </row>
     <row r="1399">
@@ -82976,16 +82876,16 @@
         <v>0</v>
       </c>
       <c r="L1399" t="n">
-        <v>130.4742857142857</v>
+        <v>127.7328571428572</v>
       </c>
       <c r="M1399" t="n">
-        <v>0.7444378750054743</v>
+        <v>0.7604151521590818</v>
       </c>
       <c r="N1399" t="n">
-        <v>0.1345859063635965</v>
+        <v>0.1374744164718777</v>
       </c>
       <c r="O1399" t="n">
-        <v>0.25223360924977</v>
+        <v>0.2576470982966682</v>
       </c>
     </row>
     <row r="1400">
@@ -83035,16 +82935,16 @@
         <v>0</v>
       </c>
       <c r="L1400" t="n">
-        <v>129.1978571428571</v>
+        <v>125.9821428571429</v>
       </c>
       <c r="M1400" t="n">
-        <v>0.5290335421308403</v>
+        <v>0.5425372076541459</v>
       </c>
       <c r="N1400" t="n">
-        <v>0.1307297224080453</v>
+        <v>0.1340666194188519</v>
       </c>
       <c r="O1400" t="n">
-        <v>0.2428832853264926</v>
+        <v>0.2490829199149539</v>
       </c>
     </row>
     <row r="1401">
@@ -83094,16 +82994,16 @@
         <v>0</v>
       </c>
       <c r="L1401" t="n">
-        <v>129.1978571428571</v>
+        <v>125.9821428571429</v>
       </c>
       <c r="M1401" t="n">
-        <v>0.5290335421308403</v>
+        <v>0.5425372076541459</v>
       </c>
       <c r="N1401" t="n">
-        <v>0.1307297224080453</v>
+        <v>0.1340666194188519</v>
       </c>
       <c r="O1401" t="n">
-        <v>0.2428832853264926</v>
+        <v>0.2490829199149539</v>
       </c>
     </row>
     <row r="1402">
@@ -83153,16 +83053,16 @@
         <v>0</v>
       </c>
       <c r="L1402" t="n">
-        <v>129.1978571428571</v>
+        <v>125.9821428571429</v>
       </c>
       <c r="M1402" t="n">
-        <v>0.5290335421308403</v>
+        <v>0.5425372076541459</v>
       </c>
       <c r="N1402" t="n">
-        <v>0.1307297224080453</v>
+        <v>0.1340666194188519</v>
       </c>
       <c r="O1402" t="n">
-        <v>0.2428832853264926</v>
+        <v>0.2490829199149539</v>
       </c>
     </row>
     <row r="1403">
@@ -83212,16 +83112,16 @@
         <v>0</v>
       </c>
       <c r="L1403" t="n">
-        <v>129.1978571428571</v>
+        <v>125.9821428571429</v>
       </c>
       <c r="M1403" t="n">
-        <v>0.5290335421308403</v>
+        <v>0.5425372076541459</v>
       </c>
       <c r="N1403" t="n">
-        <v>0.1307297224080453</v>
+        <v>0.1340666194188519</v>
       </c>
       <c r="O1403" t="n">
-        <v>0.2428832853264926</v>
+        <v>0.2490829199149539</v>
       </c>
     </row>
     <row r="1404">
@@ -83271,16 +83171,16 @@
         <v>0</v>
       </c>
       <c r="L1404" t="n">
-        <v>129.1978571428571</v>
+        <v>125.9821428571429</v>
       </c>
       <c r="M1404" t="n">
-        <v>0.5290335421308403</v>
+        <v>0.5425372076541459</v>
       </c>
       <c r="N1404" t="n">
-        <v>0.1307297224080453</v>
+        <v>0.1340666194188519</v>
       </c>
       <c r="O1404" t="n">
-        <v>0.2428832853264926</v>
+        <v>0.2490829199149539</v>
       </c>
     </row>
     <row r="1405">
@@ -83330,16 +83230,16 @@
         <v>0</v>
       </c>
       <c r="L1405" t="n">
-        <v>131.7571428571429</v>
+        <v>129.2628571428572</v>
       </c>
       <c r="M1405" t="n">
-        <v>0.5485850590914018</v>
+        <v>0.5591706821095441</v>
       </c>
       <c r="N1405" t="n">
-        <v>0.04925729155372437</v>
+        <v>0.05020777153971972</v>
       </c>
       <c r="O1405" t="n">
-        <v>0.1757020492247641</v>
+        <v>0.1790924362318199</v>
       </c>
     </row>
     <row r="1406">
@@ -83389,16 +83289,16 @@
         <v>0</v>
       </c>
       <c r="L1406" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1406" t="n">
-        <v>0.286192787723258</v>
+        <v>0.2938347503584447</v>
       </c>
       <c r="N1406" t="n">
-        <v>0.04537818590318358</v>
+        <v>0.04658988101221621</v>
       </c>
       <c r="O1406" t="n">
-        <v>0.1655690566737779</v>
+        <v>0.169990106395924</v>
       </c>
     </row>
     <row r="1407">
@@ -83448,16 +83348,16 @@
         <v>0</v>
       </c>
       <c r="L1407" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1407" t="n">
-        <v>0.286192787723258</v>
+        <v>0.2938347503584447</v>
       </c>
       <c r="N1407" t="n">
-        <v>0.04537818590318358</v>
+        <v>0.04658988101221621</v>
       </c>
       <c r="O1407" t="n">
-        <v>0.1655690566737779</v>
+        <v>0.169990106395924</v>
       </c>
     </row>
     <row r="1408">
@@ -83507,16 +83407,16 @@
         <v>0</v>
       </c>
       <c r="L1408" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1408" t="n">
-        <v>0.286192787723258</v>
+        <v>0.2938347503584447</v>
       </c>
       <c r="N1408" t="n">
-        <v>0.04537818590318358</v>
+        <v>0.04658988101221621</v>
       </c>
       <c r="O1408" t="n">
-        <v>0.1655690566737779</v>
+        <v>0.169990106395924</v>
       </c>
     </row>
     <row r="1409">
@@ -83566,16 +83466,16 @@
         <v>0</v>
       </c>
       <c r="L1409" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1409" t="n">
-        <v>0.286192787723258</v>
+        <v>0.2938347503584447</v>
       </c>
       <c r="N1409" t="n">
-        <v>0.04537818590318358</v>
+        <v>0.04658988101221621</v>
       </c>
       <c r="O1409" t="n">
-        <v>0.1655690566737779</v>
+        <v>0.169990106395924</v>
       </c>
     </row>
     <row r="1410">
@@ -83625,16 +83525,16 @@
         <v>0</v>
       </c>
       <c r="L1410" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1410" t="n">
-        <v>0.286192787723258</v>
+        <v>0.2938347503584447</v>
       </c>
       <c r="N1410" t="n">
-        <v>0.04537818590318358</v>
+        <v>0.04658988101221621</v>
       </c>
       <c r="O1410" t="n">
-        <v>0.1655690566737779</v>
+        <v>0.169990106395924</v>
       </c>
     </row>
     <row r="1411">
@@ -83684,16 +83584,16 @@
         <v>0</v>
       </c>
       <c r="L1411" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1411" t="n">
-        <v>0.3444846386131981</v>
+        <v>0.3536831189719116</v>
       </c>
       <c r="N1411" t="n">
-        <v>0.05576683259644025</v>
+        <v>0.05725592690372517</v>
       </c>
       <c r="O1411" t="n">
-        <v>0.07199909305465377</v>
+        <v>0.07392162360920791</v>
       </c>
     </row>
     <row r="1412">
@@ -83743,16 +83643,16 @@
         <v>0</v>
       </c>
       <c r="L1412" t="n">
-        <v>138.6128571428571</v>
+        <v>135.0078571428572</v>
       </c>
       <c r="M1412" t="n">
-        <v>0.3408053262426697</v>
+        <v>0.3499055610520022</v>
       </c>
       <c r="N1412" t="n">
-        <v>0.03910171185934102</v>
+        <v>0.04014581161942955</v>
       </c>
       <c r="O1412" t="n">
-        <v>0.05843613764956868</v>
+        <v>0.05999650813973788</v>
       </c>
     </row>
     <row r="1413">
@@ -83802,16 +83702,16 @@
         <v>0</v>
       </c>
       <c r="L1413" t="n">
-        <v>136.135</v>
+        <v>133.5514285714287</v>
       </c>
       <c r="M1413" t="n">
-        <v>0.2368237411393103</v>
+        <v>0.2414051301799199</v>
       </c>
       <c r="N1413" t="n">
-        <v>0.1129026334153598</v>
+        <v>0.1150867509573625</v>
       </c>
       <c r="O1413" t="n">
-        <v>0.1399346237191024</v>
+        <v>0.1426416789679737</v>
       </c>
     </row>
     <row r="1414">
@@ -83861,16 +83761,16 @@
         <v>0</v>
       </c>
       <c r="L1414" t="n">
-        <v>136.135</v>
+        <v>133.5514285714287</v>
       </c>
       <c r="M1414" t="n">
-        <v>0.5969074815440557</v>
+        <v>0.6084547418864853</v>
       </c>
       <c r="N1414" t="n">
-        <v>0.0520806552319389</v>
+        <v>0.05308816293348733</v>
       </c>
       <c r="O1414" t="n">
-        <v>0.05634113196459398</v>
+        <v>0.05743105919602932</v>
       </c>
     </row>
     <row r="1415">
@@ -83881,7 +83781,7 @@
       </c>
       <c r="B1415" t="inlineStr">
         <is>
-          <t>Durable Goods Orders m/m</t>
+          <t>GDP q/q</t>
         </is>
       </c>
       <c r="C1415" t="inlineStr">
@@ -83920,16 +83820,16 @@
         <v>0</v>
       </c>
       <c r="L1415" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1415" t="n">
-        <v>0.4646395104226431</v>
+        <v>0.474007514019108</v>
       </c>
       <c r="N1415" t="n">
-        <v>0.0621916236374068</v>
+        <v>0.06344552336146442</v>
       </c>
       <c r="O1415" t="n">
-        <v>0.1587301587301588</v>
+        <v>0.1619304563038606</v>
       </c>
     </row>
     <row r="1416">
@@ -83940,7 +83840,7 @@
       </c>
       <c r="B1416" t="inlineStr">
         <is>
-          <t>GDP q/q</t>
+          <t>GDP Sales q/q</t>
         </is>
       </c>
       <c r="C1416" t="inlineStr">
@@ -83979,16 +83879,16 @@
         <v>0</v>
       </c>
       <c r="L1416" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1416" t="n">
-        <v>0.4646395104226431</v>
+        <v>0.474007514019108</v>
       </c>
       <c r="N1416" t="n">
-        <v>0.0621916236374068</v>
+        <v>0.06344552336146442</v>
       </c>
       <c r="O1416" t="n">
-        <v>0.1587301587301588</v>
+        <v>0.1619304563038606</v>
       </c>
     </row>
     <row r="1417">
@@ -83999,7 +83899,7 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>GDP Sales q/q</t>
+          <t>Core PCE Price Index m/m</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
@@ -84038,16 +83938,16 @@
         <v>0</v>
       </c>
       <c r="L1417" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1417" t="n">
-        <v>0.4646395104226431</v>
+        <v>0.474007514019108</v>
       </c>
       <c r="N1417" t="n">
-        <v>0.0621916236374068</v>
+        <v>0.06344552336146442</v>
       </c>
       <c r="O1417" t="n">
-        <v>0.1587301587301588</v>
+        <v>0.1619304563038606</v>
       </c>
     </row>
     <row r="1418">
@@ -84058,7 +83958,7 @@
       </c>
       <c r="B1418" t="inlineStr">
         <is>
-          <t>Core PCE Price Index m/m</t>
+          <t>Core PCE Price Index y/y</t>
         </is>
       </c>
       <c r="C1418" t="inlineStr">
@@ -84097,16 +83997,16 @@
         <v>0</v>
       </c>
       <c r="L1418" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1418" t="n">
-        <v>0.4646395104226431</v>
+        <v>0.474007514019108</v>
       </c>
       <c r="N1418" t="n">
-        <v>0.0621916236374068</v>
+        <v>0.06344552336146442</v>
       </c>
       <c r="O1418" t="n">
-        <v>0.1587301587301588</v>
+        <v>0.1619304563038606</v>
       </c>
     </row>
     <row r="1419">
@@ -84117,7 +84017,7 @@
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Core PCE Price Index y/y</t>
+          <t>Durable Goods Orders m/m</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
@@ -84156,16 +84056,16 @@
         <v>0</v>
       </c>
       <c r="L1419" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1419" t="n">
-        <v>0.4646395104226431</v>
+        <v>0.474007514019108</v>
       </c>
       <c r="N1419" t="n">
-        <v>0.0621916236374068</v>
+        <v>0.06344552336146442</v>
       </c>
       <c r="O1419" t="n">
-        <v>0.1587301587301588</v>
+        <v>0.1619304563038606</v>
       </c>
     </row>
     <row r="1420">
@@ -84215,16 +84115,16 @@
         <v>1</v>
       </c>
       <c r="L1420" t="n">
-        <v>130.725</v>
+        <v>128.1414285714287</v>
       </c>
       <c r="M1420" t="n">
-        <v>0.4133868808567605</v>
+        <v>0.4217215353571386</v>
       </c>
       <c r="N1420" t="n">
-        <v>0.3255689424364124</v>
+        <v>0.3321330226646895</v>
       </c>
       <c r="O1420" t="n">
-        <v>0.2556511761331039</v>
+        <v>0.2608055831168685</v>
       </c>
     </row>
     <row r="1421">
@@ -84274,16 +84174,16 @@
         <v>0</v>
       </c>
       <c r="L1421" t="n">
-        <v>128.555</v>
+        <v>126.7057142857144</v>
       </c>
       <c r="M1421" t="n">
-        <v>1.404223873050446</v>
+        <v>1.42471869574041</v>
       </c>
       <c r="N1421" t="n">
-        <v>0.1243047722764576</v>
+        <v>0.1261190159424538</v>
       </c>
       <c r="O1421" t="n">
-        <v>0.2731126755085372</v>
+        <v>0.2770987890950908</v>
       </c>
     </row>
     <row r="1422">
@@ -84333,16 +84233,16 @@
         <v>0</v>
       </c>
       <c r="L1422" t="n">
-        <v>128.555</v>
+        <v>126.7057142857144</v>
       </c>
       <c r="M1422" t="n">
-        <v>1.254638092645171</v>
+        <v>1.272949692200148</v>
       </c>
       <c r="N1422" t="n">
-        <v>0.07708762786356035</v>
+        <v>0.07821273141362432</v>
       </c>
       <c r="O1422" t="n">
-        <v>0.1102251954416398</v>
+        <v>0.1118339459264437</v>
       </c>
     </row>
     <row r="1423">
@@ -84392,16 +84292,16 @@
         <v>0</v>
       </c>
       <c r="L1423" t="n">
-        <v>128.555</v>
+        <v>126.7057142857144</v>
       </c>
       <c r="M1423" t="n">
-        <v>0.2966045661390067</v>
+        <v>0.3009335468013618</v>
       </c>
       <c r="N1423" t="n">
-        <v>0.1394733771537474</v>
+        <v>0.1415090085011387</v>
       </c>
       <c r="O1423" t="n">
-        <v>0.1696550114736883</v>
+        <v>0.1721311475409835</v>
       </c>
     </row>
     <row r="1424">
@@ -84451,16 +84351,16 @@
         <v>0</v>
       </c>
       <c r="L1424" t="n">
-        <v>130.2414285714286</v>
+        <v>129.6971428571429</v>
       </c>
       <c r="M1424" t="n">
-        <v>2.162292007151554</v>
+        <v>2.17136625985813</v>
       </c>
       <c r="N1424" t="n">
-        <v>0.2101481863352675</v>
+        <v>0.2110300920826539</v>
       </c>
       <c r="O1424" t="n">
-        <v>0.3401375467538308</v>
+        <v>0.3415649645327574</v>
       </c>
     </row>
     <row r="1425">
@@ -84510,16 +84410,16 @@
         <v>0</v>
       </c>
       <c r="L1425" t="n">
-        <v>130.2414285714286</v>
+        <v>129.6971428571429</v>
       </c>
       <c r="M1425" t="n">
-        <v>2.162292007151554</v>
+        <v>2.17136625985813</v>
       </c>
       <c r="N1425" t="n">
-        <v>0.2101481863352675</v>
+        <v>0.2110300920826539</v>
       </c>
       <c r="O1425" t="n">
-        <v>0.3401375467538308</v>
+        <v>0.3415649645327574</v>
       </c>
     </row>
     <row r="1426">
@@ -84569,16 +84469,16 @@
         <v>1</v>
       </c>
       <c r="L1426" t="n">
-        <v>130.2414285714286</v>
+        <v>129.6971428571429</v>
       </c>
       <c r="M1426" t="n">
-        <v>0.6838837762836051</v>
+        <v>0.6867537560029955</v>
       </c>
       <c r="N1426" t="n">
-        <v>0.2275005758536345</v>
+        <v>0.2284553024628804</v>
       </c>
       <c r="O1426" t="n">
-        <v>0.3489673024822034</v>
+        <v>0.3504317751244655</v>
       </c>
     </row>
     <row r="1427">
@@ -84628,16 +84528,16 @@
         <v>0</v>
       </c>
       <c r="L1427" t="n">
-        <v>164.4449999999999</v>
+        <v>165.1121428571428</v>
       </c>
       <c r="M1427" t="n">
-        <v>0.3898567910243549</v>
+        <v>0.3882815575561199</v>
       </c>
       <c r="N1427" t="n">
-        <v>0.09717534738058323</v>
+        <v>0.0967827061261394</v>
       </c>
       <c r="O1427" t="n">
-        <v>0.06859436285688228</v>
+        <v>0.06831720432433369</v>
       </c>
     </row>
     <row r="1428">
@@ -84687,16 +84587,16 @@
         <v>0</v>
       </c>
       <c r="L1428" t="n">
-        <v>167.822857142857</v>
+        <v>168.49</v>
       </c>
       <c r="M1428" t="n">
-        <v>0.3042493785964795</v>
+        <v>0.3030446910795894</v>
       </c>
       <c r="N1428" t="n">
-        <v>0.08306377472845522</v>
+        <v>0.08273488040833285</v>
       </c>
       <c r="O1428" t="n">
-        <v>0.1868636998195377</v>
+        <v>0.186123805567096</v>
       </c>
     </row>
     <row r="1429">
@@ -84746,16 +84646,16 @@
         <v>0</v>
       </c>
       <c r="L1429" t="n">
-        <v>180.8628571428571</v>
+        <v>178.8907142857142</v>
       </c>
       <c r="M1429" t="n">
-        <v>0.3760307731193329</v>
+        <v>0.3801762448741651</v>
       </c>
       <c r="N1429" t="n">
-        <v>0.09244573631164894</v>
+        <v>0.09346488478600265</v>
       </c>
       <c r="O1429" t="n">
-        <v>0.2216043726896465</v>
+        <v>0.2240474032430016</v>
       </c>
     </row>
     <row r="1430">
@@ -84805,16 +84705,16 @@
         <v>0</v>
       </c>
       <c r="L1430" t="n">
-        <v>180.8628571428571</v>
+        <v>178.8907142857142</v>
       </c>
       <c r="M1430" t="n">
-        <v>0.4433193264035893</v>
+        <v>0.4482066065874218</v>
       </c>
       <c r="N1430" t="n">
-        <v>0.1350194306656978</v>
+        <v>0.1365079238321881</v>
       </c>
       <c r="O1430" t="n">
-        <v>0.1187087295820038</v>
+        <v>0.1200174088729352</v>
       </c>
     </row>
     <row r="1431">
@@ -84864,16 +84764,16 @@
         <v>0</v>
       </c>
       <c r="L1431" t="n">
-        <v>180.8628571428571</v>
+        <v>178.8907142857142</v>
       </c>
       <c r="M1431" t="n">
-        <v>0.4433193264035893</v>
+        <v>0.4482066065874218</v>
       </c>
       <c r="N1431" t="n">
-        <v>0.1350194306656978</v>
+        <v>0.1365079238321881</v>
       </c>
       <c r="O1431" t="n">
-        <v>0.1187087295820038</v>
+        <v>0.1200174088729352</v>
       </c>
     </row>
     <row r="1432">
@@ -84923,16 +84823,16 @@
         <v>0</v>
       </c>
       <c r="L1432" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1432" t="n">
-        <v>0.4283325397581185</v>
+        <v>0.4328852342895861</v>
       </c>
       <c r="N1432" t="n">
-        <v>0.05178173507285024</v>
+        <v>0.05233211684452044</v>
       </c>
       <c r="O1432" t="n">
-        <v>0.1107627844967147</v>
+        <v>0.1119400686777229</v>
       </c>
     </row>
     <row r="1433">
@@ -84982,16 +84882,16 @@
         <v>0</v>
       </c>
       <c r="L1433" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1433" t="n">
-        <v>0.4283325397581185</v>
+        <v>0.4328852342895861</v>
       </c>
       <c r="N1433" t="n">
-        <v>0.09225788020188559</v>
+        <v>0.09323847800311057</v>
       </c>
       <c r="O1433" t="n">
-        <v>0.1211084658603943</v>
+        <v>0.122395713031829</v>
       </c>
     </row>
     <row r="1434">
@@ -85041,16 +84941,16 @@
         <v>0</v>
       </c>
       <c r="L1434" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1434" t="n">
-        <v>0.4283325397581185</v>
+        <v>0.4328852342895861</v>
       </c>
       <c r="N1434" t="n">
-        <v>0.09225788020188559</v>
+        <v>0.09323847800311057</v>
       </c>
       <c r="O1434" t="n">
-        <v>0.1211084658603943</v>
+        <v>0.122395713031829</v>
       </c>
     </row>
     <row r="1435">
@@ -85100,16 +85000,16 @@
         <v>0</v>
       </c>
       <c r="L1435" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1435" t="n">
-        <v>0.2848795352823543</v>
+        <v>0.2879074852558478</v>
       </c>
       <c r="N1435" t="n">
-        <v>0.07567279306732697</v>
+        <v>0.07647710999214676</v>
       </c>
       <c r="O1435" t="n">
-        <v>0.1318274450052377</v>
+        <v>0.1332286229038667</v>
       </c>
     </row>
     <row r="1436">
@@ -85159,16 +85059,16 @@
         <v>1</v>
       </c>
       <c r="L1436" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1436" t="n">
-        <v>0.1775830873250168</v>
+        <v>0.1794705963874903</v>
       </c>
       <c r="N1436" t="n">
-        <v>0.07903247309780026</v>
+        <v>0.07987249965353171</v>
       </c>
       <c r="O1436" t="n">
-        <v>0.1320940862774975</v>
+        <v>0.1334980982738178</v>
       </c>
     </row>
     <row r="1437">
@@ -85218,16 +85118,16 @@
         <v>1</v>
       </c>
       <c r="L1437" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1437" t="n">
-        <v>0.1775830873250168</v>
+        <v>0.1794705963874903</v>
       </c>
       <c r="N1437" t="n">
-        <v>0.07903247309780026</v>
+        <v>0.07987249965353171</v>
       </c>
       <c r="O1437" t="n">
-        <v>0.1320940862774975</v>
+        <v>0.1334980982738178</v>
       </c>
     </row>
     <row r="1438">
@@ -85277,16 +85177,16 @@
         <v>0</v>
       </c>
       <c r="L1438" t="n">
-        <v>187.517857142857</v>
+        <v>185.5457142857142</v>
       </c>
       <c r="M1438" t="n">
-        <v>0.2807199314351016</v>
+        <v>0.2837036694846093</v>
       </c>
       <c r="N1438" t="n">
-        <v>0.1307608799161985</v>
+        <v>0.1321507214240619</v>
       </c>
       <c r="O1438" t="n">
-        <v>0.1330006666031807</v>
+        <v>0.1344143145316519</v>
       </c>
     </row>
     <row r="1439">
@@ -85336,16 +85236,16 @@
         <v>0</v>
       </c>
       <c r="L1439" t="n">
-        <v>195.442857142857</v>
+        <v>193.4707142857142</v>
       </c>
       <c r="M1439" t="n">
-        <v>0.4963087493604272</v>
+        <v>0.5013678703679777</v>
       </c>
       <c r="N1439" t="n">
-        <v>0.09035889189386748</v>
+        <v>0.09127996485256172</v>
       </c>
       <c r="O1439" t="n">
-        <v>0.06666910313573574</v>
+        <v>0.06734869433912113</v>
       </c>
     </row>
     <row r="1440">
@@ -85395,7 +85295,7 @@
         <v>0</v>
       </c>
       <c r="L1440" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1440" t="n">
         <v>0</v>
@@ -85454,7 +85354,7 @@
         <v>0</v>
       </c>
       <c r="L1441" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1441" t="n">
         <v>0</v>
@@ -85513,7 +85413,7 @@
         <v>0</v>
       </c>
       <c r="L1442" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1442" t="n">
         <v>0</v>
@@ -85572,7 +85472,7 @@
         <v>0</v>
       </c>
       <c r="L1443" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1443" t="n">
         <v>0</v>
@@ -85631,7 +85531,7 @@
         <v>1</v>
       </c>
       <c r="L1444" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1444" t="n">
         <v>0</v>
@@ -85690,7 +85590,7 @@
         <v>1</v>
       </c>
       <c r="L1445" t="n">
-        <v>207.9792857142856</v>
+        <v>206.0071428571428</v>
       </c>
       <c r="M1445" t="n">
         <v>0</v>
@@ -85749,16 +85649,16 @@
         <v>0</v>
       </c>
       <c r="L1446" t="n">
-        <v>176.982857142857</v>
+        <v>175.0107142857141</v>
       </c>
       <c r="M1446" t="n">
-        <v>0.3702618494123728</v>
+        <v>0.3744342183131648</v>
       </c>
       <c r="N1446" t="n">
-        <v>0.07718261655689017</v>
+        <v>0.07805236414097103</v>
       </c>
       <c r="O1446" t="n">
-        <v>0.1119317448017565</v>
+        <v>0.1131930698120524</v>
       </c>
     </row>
     <row r="1447">
@@ -85808,16 +85708,16 @@
         <v>0</v>
       </c>
       <c r="L1447" t="n">
-        <v>169.2599999999998</v>
+        <v>167.287857142857</v>
       </c>
       <c r="M1447" t="n">
-        <v>0.308283114734728</v>
+        <v>0.3119174391446739</v>
       </c>
       <c r="N1447" t="n">
-        <v>0.1111898853834339</v>
+        <v>0.1125006938425213</v>
       </c>
       <c r="O1447" t="n">
-        <v>0.120583717357911</v>
+        <v>0.1220052689333613</v>
       </c>
     </row>
     <row r="1448">
@@ -85867,16 +85767,16 @@
         <v>0</v>
       </c>
       <c r="L1448" t="n">
-        <v>169.2599999999998</v>
+        <v>167.287857142857</v>
       </c>
       <c r="M1448" t="n">
-        <v>0.4430462011107177</v>
+        <v>0.448269236517039</v>
       </c>
       <c r="N1448" t="n">
-        <v>0.03444405057308287</v>
+        <v>0.03485010866641335</v>
       </c>
       <c r="O1448" t="n">
-        <v>0.05671747607231484</v>
+        <v>0.05738611375601513</v>
       </c>
     </row>
     <row r="1449">
@@ -85926,16 +85826,16 @@
         <v>0</v>
       </c>
       <c r="L1449" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1449" t="n">
-        <v>0.3198746613571827</v>
+        <v>0.3253017547208175</v>
       </c>
       <c r="N1449" t="n">
-        <v>0.03849920031334664</v>
+        <v>0.03915238976461268</v>
       </c>
       <c r="O1449" t="n">
-        <v>0.07282860593400142</v>
+        <v>0.07406423879804327</v>
       </c>
     </row>
     <row r="1450">
@@ -85985,16 +85885,16 @@
         <v>0</v>
       </c>
       <c r="L1450" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1450" t="n">
-        <v>0.3198746613571827</v>
+        <v>0.3253017547208175</v>
       </c>
       <c r="N1450" t="n">
-        <v>0.03849920031334664</v>
+        <v>0.03915238976461268</v>
       </c>
       <c r="O1450" t="n">
-        <v>0.07282860593400142</v>
+        <v>0.07406423879804327</v>
       </c>
     </row>
     <row r="1451">
@@ -86044,16 +85944,16 @@
         <v>0</v>
       </c>
       <c r="L1451" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1451" t="n">
-        <v>0.3198746613571827</v>
+        <v>0.3253017547208175</v>
       </c>
       <c r="N1451" t="n">
-        <v>0.03849920031334664</v>
+        <v>0.03915238976461268</v>
       </c>
       <c r="O1451" t="n">
-        <v>0.07282860593400142</v>
+        <v>0.07406423879804327</v>
       </c>
     </row>
     <row r="1452">
@@ -86103,16 +86003,16 @@
         <v>0</v>
       </c>
       <c r="L1452" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1452" t="n">
-        <v>0.3198746613571827</v>
+        <v>0.3253017547208175</v>
       </c>
       <c r="N1452" t="n">
-        <v>0.03849920031334664</v>
+        <v>0.03915238976461268</v>
       </c>
       <c r="O1452" t="n">
-        <v>0.07282860593400142</v>
+        <v>0.07406423879804327</v>
       </c>
     </row>
     <row r="1453">
@@ -86162,16 +86062,16 @@
         <v>0</v>
       </c>
       <c r="L1453" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1453" t="n">
-        <v>0.3198746613571827</v>
+        <v>0.3253017547208175</v>
       </c>
       <c r="N1453" t="n">
-        <v>0.03849920031334664</v>
+        <v>0.03915238976461268</v>
       </c>
       <c r="O1453" t="n">
-        <v>0.07282860593400142</v>
+        <v>0.07406423879804327</v>
       </c>
     </row>
     <row r="1454">
@@ -86221,16 +86121,16 @@
         <v>0</v>
       </c>
       <c r="L1454" t="n">
-        <v>175.0685714285713</v>
+        <v>172.147857142857</v>
       </c>
       <c r="M1454" t="n">
-        <v>0.3772236185005063</v>
+        <v>0.3836237121743356</v>
       </c>
       <c r="N1454" t="n">
-        <v>0.03227306851193005</v>
+        <v>0.0328206234673682</v>
       </c>
       <c r="O1454" t="n">
-        <v>0.06580278747919188</v>
+        <v>0.06691921811399675</v>
       </c>
     </row>
     <row r="1455">
@@ -86280,16 +86180,16 @@
         <v>0</v>
       </c>
       <c r="L1455" t="n">
-        <v>150.8921428571428</v>
+        <v>147.9714285714285</v>
       </c>
       <c r="M1455" t="n">
-        <v>0.2676746398799523</v>
+        <v>0.2729581000193089</v>
       </c>
       <c r="N1455" t="n">
-        <v>0.05772335016970499</v>
+        <v>0.05886271480980889</v>
       </c>
       <c r="O1455" t="n">
-        <v>0.1356598137742664</v>
+        <v>0.1383375168951536</v>
       </c>
     </row>
     <row r="1456">
@@ -86339,16 +86239,16 @@
         <v>0</v>
       </c>
       <c r="L1456" t="n">
-        <v>150.8921428571428</v>
+        <v>147.9714285714285</v>
       </c>
       <c r="M1456" t="n">
-        <v>0.2676746398799523</v>
+        <v>0.2729581000193089</v>
       </c>
       <c r="N1456" t="n">
-        <v>0.05772335016970499</v>
+        <v>0.05886271480980889</v>
       </c>
       <c r="O1456" t="n">
-        <v>0.1356598137742664</v>
+        <v>0.1383375168951536</v>
       </c>
     </row>
     <row r="1457">
@@ -86398,16 +86298,16 @@
         <v>0</v>
       </c>
       <c r="L1457" t="n">
-        <v>150.8921428571428</v>
+        <v>147.9714285714285</v>
       </c>
       <c r="M1457" t="n">
-        <v>0.2676746398799523</v>
+        <v>0.2729581000193089</v>
       </c>
       <c r="N1457" t="n">
-        <v>0.05772335016970499</v>
+        <v>0.05886271480980889</v>
       </c>
       <c r="O1457" t="n">
-        <v>0.1356598137742664</v>
+        <v>0.1383375168951536</v>
       </c>
     </row>
     <row r="1458">
@@ -86457,16 +86357,16 @@
         <v>0</v>
       </c>
       <c r="L1458" t="n">
-        <v>150.8921428571428</v>
+        <v>147.9714285714285</v>
       </c>
       <c r="M1458" t="n">
-        <v>0.2676746398799523</v>
+        <v>0.2729581000193089</v>
       </c>
       <c r="N1458" t="n">
-        <v>0.05772335016970499</v>
+        <v>0.05886271480980889</v>
       </c>
       <c r="O1458" t="n">
-        <v>0.1356598137742664</v>
+        <v>0.1383375168951536</v>
       </c>
     </row>
     <row r="1459">
@@ -86516,16 +86416,16 @@
         <v>0</v>
       </c>
       <c r="L1459" t="n">
-        <v>150.8921428571428</v>
+        <v>147.9714285714285</v>
       </c>
       <c r="M1459" t="n">
-        <v>0.2676746398799523</v>
+        <v>0.2729581000193089</v>
       </c>
       <c r="N1459" t="n">
-        <v>0.05772335016970499</v>
+        <v>0.05886271480980889</v>
       </c>
       <c r="O1459" t="n">
-        <v>0.1356598137742664</v>
+        <v>0.1383375168951536</v>
       </c>
     </row>
     <row r="1460">
@@ -86575,16 +86475,16 @@
         <v>0</v>
       </c>
       <c r="L1460" t="n">
-        <v>130.295</v>
+        <v>127.3742857142857</v>
       </c>
       <c r="M1460" t="n">
-        <v>0.3135193215395832</v>
+        <v>0.3207083735223526</v>
       </c>
       <c r="N1460" t="n">
-        <v>0.178978471929084</v>
+        <v>0.1830824790830174</v>
       </c>
       <c r="O1460" t="n">
-        <v>0.1082159714494033</v>
+        <v>0.1106973822929051</v>
       </c>
     </row>
     <row r="1461">
@@ -86634,16 +86534,16 @@
         <v>0</v>
       </c>
       <c r="L1461" t="n">
-        <v>123.6592857142857</v>
+        <v>124.02</v>
       </c>
       <c r="M1461" t="n">
-        <v>0.3530668946356059</v>
+        <v>0.3520399935494276</v>
       </c>
       <c r="N1461" t="n">
-        <v>0.06550256176244637</v>
+        <v>0.06531204644412192</v>
       </c>
       <c r="O1461" t="n">
-        <v>0.0828081768453643</v>
+        <v>0.08256732785034673</v>
       </c>
     </row>
     <row r="1462">
@@ -86693,16 +86593,16 @@
         <v>0</v>
       </c>
       <c r="L1462" t="n">
-        <v>116.8221428571427</v>
+        <v>117.182857142857</v>
       </c>
       <c r="M1462" t="n">
-        <v>0.3795513326118463</v>
+        <v>0.3783829911737459</v>
       </c>
       <c r="N1462" t="n">
-        <v>0.04442650916227971</v>
+        <v>0.04428975471790125</v>
       </c>
       <c r="O1462" t="n">
-        <v>0.08756901516958022</v>
+        <v>0.08729945872141227</v>
       </c>
     </row>
     <row r="1463">
@@ -87893,7 +87793,7 @@
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>JOLTS Job Openings</t>
+          <t>ISM Non-Manufacturing PMI</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
@@ -87952,7 +87852,7 @@
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>ISM Non-Manufacturing PMI</t>
+          <t>ISM Non-Manufacturing Prices Paid</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
@@ -88011,7 +87911,7 @@
       </c>
       <c r="B1485" t="inlineStr">
         <is>
-          <t>ISM Non-Manufacturing Prices Paid</t>
+          <t>JOLTS Job Openings</t>
         </is>
       </c>
       <c r="C1485" t="inlineStr">
@@ -89545,7 +89445,7 @@
       </c>
       <c r="B1511" t="inlineStr">
         <is>
-          <t>Durable Goods Orders m/m</t>
+          <t>GDP q/q</t>
         </is>
       </c>
       <c r="C1511" t="inlineStr">
@@ -89604,7 +89504,7 @@
       </c>
       <c r="B1512" t="inlineStr">
         <is>
-          <t>GDP q/q</t>
+          <t>GDP Sales q/q</t>
         </is>
       </c>
       <c r="C1512" t="inlineStr">
@@ -89663,7 +89563,7 @@
       </c>
       <c r="B1513" t="inlineStr">
         <is>
-          <t>GDP Sales q/q</t>
+          <t>Core PCE Price Index m/m</t>
         </is>
       </c>
       <c r="C1513" t="inlineStr">
@@ -89722,7 +89622,7 @@
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Core PCE Price Index m/m</t>
+          <t>Core PCE Price Index y/y</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
@@ -89781,7 +89681,7 @@
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Core PCE Price Index y/y</t>
+          <t>Durable Goods Orders m/m</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
@@ -91964,7 +91864,7 @@
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>Durable Goods Orders m/m</t>
+          <t>GDP q/q</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
@@ -92023,7 +91923,7 @@
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>GDP q/q</t>
+          <t>GDP Sales q/q</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
@@ -92082,7 +91982,7 @@
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>GDP Sales q/q</t>
+          <t>Core PCE Price Index m/m</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
@@ -92141,7 +92041,7 @@
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>Core PCE Price Index m/m</t>
+          <t>Core PCE Price Index y/y</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
@@ -92200,7 +92100,7 @@
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Core PCE Price Index y/y</t>
+          <t>Durable Goods Orders m/m</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
@@ -96684,7 +96584,7 @@
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>Durable Goods Orders m/m</t>
+          <t>GDP q/q</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
@@ -96743,7 +96643,7 @@
       </c>
       <c r="B1633" t="inlineStr">
         <is>
-          <t>GDP q/q</t>
+          <t>GDP Sales q/q</t>
         </is>
       </c>
       <c r="C1633" t="inlineStr">
@@ -96802,7 +96702,7 @@
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>GDP Sales q/q</t>
+          <t>Core PCE Price Index m/m</t>
         </is>
       </c>
       <c r="C1634" t="inlineStr">
@@ -96861,7 +96761,7 @@
       </c>
       <c r="B1635" t="inlineStr">
         <is>
-          <t>Core PCE Price Index m/m</t>
+          <t>Core PCE Price Index y/y</t>
         </is>
       </c>
       <c r="C1635" t="inlineStr">
@@ -96920,7 +96820,7 @@
       </c>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>Core PCE Price Index y/y</t>
+          <t>Durable Goods Orders m/m</t>
         </is>
       </c>
       <c r="C1636" t="inlineStr">
@@ -97913,6 +97813,655 @@
       </c>
       <c r="O1652" t="n">
         <v>0.9519537127960945</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>10-Year Note Auction</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D1653" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1653" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1653" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1653" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1653" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1653" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="K1653" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1653" t="n">
+        <v>91.6807142857142</v>
+      </c>
+      <c r="M1653" t="n">
+        <v>0.6440831145356951</v>
+      </c>
+      <c r="N1653" t="n">
+        <v>0.05453709691242126</v>
+      </c>
+      <c r="O1653" t="n">
+        <v>0.1314344035589353</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Initial Jobless Claims</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1654" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1654" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1654" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1654" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1654" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="K1654" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1654" t="n">
+        <v>92.16071428571422</v>
+      </c>
+      <c r="M1654" t="n">
+        <v>0.7485836078279408</v>
+      </c>
+      <c r="N1654" t="n">
+        <v>0.1297732997481109</v>
+      </c>
+      <c r="O1654" t="n">
+        <v>0.5241929858554548</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>PPI m/m</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1655" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1655" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1655" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1655" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I1655" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1655" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="K1655" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1655" t="n">
+        <v>92.16071428571422</v>
+      </c>
+      <c r="M1655" t="n">
+        <v>0.7485836078279408</v>
+      </c>
+      <c r="N1655" t="n">
+        <v>0.1297732997481109</v>
+      </c>
+      <c r="O1655" t="n">
+        <v>0.5241929858554548</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Existing Home Sales</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="D1656" t="b">
+        <v>1</v>
+      </c>
+      <c r="E1656" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F1656" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1656" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="I1656" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1656" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="K1656" t="b">
+        <v>1</v>
+      </c>
+      <c r="L1656" t="n">
+        <v>92.16071428571422</v>
+      </c>
+      <c r="M1656" t="n">
+        <v>0.4261034683200933</v>
+      </c>
+      <c r="N1656" t="n">
+        <v>0.1307498546793258</v>
+      </c>
+      <c r="O1656" t="n">
+        <v>0.2291648905250922</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>EIA Crude Oil Stocks Change</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D1657" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1657" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1657" t="n">
+        <v>76.29000000000001</v>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="H1657" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="I1657" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="J1657" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="K1657" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1657" t="n">
+        <v>92.16071428571422</v>
+      </c>
+      <c r="M1657" t="n">
+        <v>0.8277930633598146</v>
+      </c>
+      <c r="N1657" t="n">
+        <v>0.07118000387521803</v>
+      </c>
+      <c r="O1657" t="n">
+        <v>0.1743693082735905</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>30-Year Bond Auction</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D1658" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1658" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1658" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1658" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="I1658" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1658" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="K1658" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1658" t="n">
+        <v>92.16071428571422</v>
+      </c>
+      <c r="M1658" t="n">
+        <v>0.7697422980042633</v>
+      </c>
+      <c r="N1658" t="n">
+        <v>0.05175741135438872</v>
+      </c>
+      <c r="O1658" t="n">
+        <v>0.09071110249951565</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>CPI m/m</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1659" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1659" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1659" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1659" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I1659" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1659" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="K1659" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1659" t="n">
+        <v>93.55714285714281</v>
+      </c>
+      <c r="M1659" t="n">
+        <v>0.3830813864712172</v>
+      </c>
+      <c r="N1659" t="n">
+        <v>0.1606504809894641</v>
+      </c>
+      <c r="O1659" t="n">
+        <v>0.8036799511375786</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>Core CPI m/m</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1660" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1660" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1660" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1660" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I1660" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1660" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="K1660" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1660" t="n">
+        <v>93.55714285714281</v>
+      </c>
+      <c r="M1660" t="n">
+        <v>0.3830813864712172</v>
+      </c>
+      <c r="N1660" t="n">
+        <v>0.1606504809894641</v>
+      </c>
+      <c r="O1660" t="n">
+        <v>0.8036799511375786</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>CPI y/y</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1661" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1661" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1661" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1661" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I1661" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1661" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="K1661" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1661" t="n">
+        <v>93.55714285714281</v>
+      </c>
+      <c r="M1661" t="n">
+        <v>0.3830813864712172</v>
+      </c>
+      <c r="N1661" t="n">
+        <v>0.1606504809894641</v>
+      </c>
+      <c r="O1661" t="n">
+        <v>0.8036799511375786</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Core CPI n.s.a. m/m</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1662" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1662" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1662" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1662" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I1662" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1662" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="K1662" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1662" t="n">
+        <v>93.55714285714281</v>
+      </c>
+      <c r="M1662" t="n">
+        <v>0.3830813864712172</v>
+      </c>
+      <c r="N1662" t="n">
+        <v>0.1606504809894641</v>
+      </c>
+      <c r="O1662" t="n">
+        <v>0.8036799511375786</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>CPI</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D1663" t="b">
+        <v>0</v>
+      </c>
+      <c r="E1663" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F1663" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="H1663" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="J1663" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="K1663" t="b">
+        <v>0</v>
+      </c>
+      <c r="L1663" t="n">
+        <v>93.55714285714281</v>
+      </c>
+      <c r="M1663" t="n">
+        <v>0.3830813864712172</v>
+      </c>
+      <c r="N1663" t="n">
+        <v>0.1606504809894641</v>
+      </c>
+      <c r="O1663" t="n">
+        <v>0.8036799511375786</v>
       </c>
     </row>
   </sheetData>
